--- a/data/trans_dic/IP16_n_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,44; 60,37</t>
+          <t>21,79; 59,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,94</t>
+          <t>0,0; 21,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 33,31</t>
+          <t>3,52; 35,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,42; 62,09</t>
+          <t>31,27; 61,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,16; 46,98</t>
+          <t>15,36; 46,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 28,76</t>
+          <t>3,04; 27,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,93</t>
+          <t>0,0; 22,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,34; 45,36</t>
+          <t>13,47; 43,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,2; 44,38</t>
+          <t>21,15; 46,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 18,75</t>
+          <t>3,32; 19,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 21,71</t>
+          <t>3,5; 21,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,06; 47,45</t>
+          <t>24,56; 47,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,0; 52,74</t>
+          <t>19,56; 53,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 33,44</t>
+          <t>7,56; 31,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,65</t>
+          <t>0,0; 26,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 39,52</t>
+          <t>11,02; 39,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 60,61</t>
+          <t>25,07; 61,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,56</t>
+          <t>0,0; 27,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 32,22</t>
+          <t>3,74; 33,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,49; 62,21</t>
+          <t>26,05; 60,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,85; 49,89</t>
+          <t>26,58; 52,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 25,27</t>
+          <t>5,24; 23,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 22,35</t>
+          <t>4,09; 22,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,72; 47,53</t>
+          <t>23,37; 47,8</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,23; 62,8</t>
+          <t>13,7; 57,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 54,62</t>
+          <t>13,25; 59,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,52; 63,23</t>
+          <t>13,6; 63,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 55,41</t>
+          <t>6,43; 51,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,62; 71,12</t>
+          <t>35,14; 70,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 48,33</t>
+          <t>5,76; 48,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,56; 57,76</t>
+          <t>18,52; 57,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,7; 62,8</t>
+          <t>34,42; 61,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 42,84</t>
+          <t>12,45; 42,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 32,05</t>
+          <t>5,71; 32,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,2; 48,6</t>
+          <t>18,46; 47,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 54,01</t>
+          <t>27,84; 53,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 27,86</t>
+          <t>10,65; 28,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 20,24</t>
+          <t>5,29; 20,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 35,36</t>
+          <t>6,67; 34,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,79; 53,49</t>
+          <t>26,79; 53,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 21,12</t>
+          <t>5,37; 19,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 20,65</t>
+          <t>3,58; 20,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,24; 48,71</t>
+          <t>24,95; 48,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,34; 50,01</t>
+          <t>31,61; 50,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 20,69</t>
+          <t>9,3; 20,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 16,83</t>
+          <t>5,49; 16,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,96; 37,45</t>
+          <t>13,29; 35,81</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,01; 60,93</t>
+          <t>23,72; 60,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 34,0</t>
+          <t>8,1; 32,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 22,67</t>
+          <t>2,88; 22,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,63; 56,68</t>
+          <t>26,34; 55,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 43,22</t>
+          <t>16,04; 43,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 34,46</t>
+          <t>9,86; 35,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,84; 38,51</t>
+          <t>10,21; 38,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,96; 41,36</t>
+          <t>17,13; 41,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,89; 45,46</t>
+          <t>22,89; 45,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 29,71</t>
+          <t>11,8; 29,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 25,82</t>
+          <t>8,61; 25,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,27; 43,92</t>
+          <t>25,03; 44,17</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,53; 82,99</t>
+          <t>27,83; 82,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,8</t>
+          <t>0,0; 53,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,95</t>
+          <t>0,0; 33,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,24; 63,79</t>
+          <t>20,33; 65,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,82; 77,77</t>
+          <t>30,58; 77,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,28; 47,79</t>
+          <t>8,96; 44,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 49,8</t>
+          <t>6,44; 50,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,71; 66,54</t>
+          <t>19,98; 65,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,14; 73,12</t>
+          <t>36,54; 73,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,89; 40,25</t>
+          <t>9,86; 41,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,68; 31,68</t>
+          <t>5,55; 31,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,83; 58,29</t>
+          <t>25,62; 57,17</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,65; 47,51</t>
+          <t>32,0; 47,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 23,15</t>
+          <t>12,42; 23,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 17,51</t>
+          <t>7,75; 17,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,91; 37,58</t>
+          <t>17,03; 37,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,49; 46,39</t>
+          <t>32,68; 46,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,72; 19,36</t>
+          <t>9,73; 20,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,53; 18,38</t>
+          <t>8,25; 18,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,26; 40,25</t>
+          <t>28,17; 41,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,94; 44,98</t>
+          <t>34,82; 44,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,74; 19,58</t>
+          <t>12,49; 19,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 16,1</t>
+          <t>9,31; 16,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,21; 36,94</t>
+          <t>23,78; 36,72</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2949; 9159</t>
+          <t>3305; 9000</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4590</t>
+          <t>0; 4479</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>543; 5277</t>
+          <t>557; 5631</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7561; 15430</t>
+          <t>7771; 15254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3254; 10083</t>
+          <t>3296; 9958</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>655; 6321</t>
+          <t>668; 6007</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3890</t>
+          <t>0; 4015</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4502; 14244</t>
+          <t>4231; 13752</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8133; 16256</t>
+          <t>7746; 16942</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1350; 8043</t>
+          <t>1425; 8247</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1154; 7292</t>
+          <t>1177; 7184</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14099; 26690</t>
+          <t>13816; 26451</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3497; 10248</t>
+          <t>3800; 10454</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1497; 7658</t>
+          <t>1731; 7215</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2837</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2583; 9261</t>
+          <t>2581; 9240</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4161; 10823</t>
+          <t>4477; 10893</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3453</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>711; 6143</t>
+          <t>713; 6335</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6222; 14614</t>
+          <t>6119; 14295</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9640; 18601</t>
+          <t>9912; 19436</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1921; 8843</t>
+          <t>1834; 8355</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1326; 6941</t>
+          <t>1270; 6878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10659; 22304</t>
+          <t>10967; 22431</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2343,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1804; 6977</t>
+          <t>1522; 6348</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1294; 6266</t>
+          <t>1520; 6871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1107; 5594</t>
+          <t>1203; 5628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>753; 5317</t>
+          <t>617; 4966</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8039; 15612</t>
+          <t>7713; 15496</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>675; 6030</t>
+          <t>719; 6067</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3038; 9990</t>
+          <t>3204; 10011</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11141; 20764</t>
+          <t>11381; 20463</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3261; 10259</t>
+          <t>2981; 10076</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1118; 6126</t>
+          <t>1091; 6158</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5164; 13070</t>
+          <t>4965; 12818</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10541; 20354</t>
+          <t>10492; 20218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4783; 13551</t>
+          <t>5178; 13875</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2527; 9407</t>
+          <t>2461; 9400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5515; 27005</t>
+          <t>5093; 26185</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10779; 20748</t>
+          <t>10391; 20799</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3118; 12441</t>
+          <t>3162; 11512</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1211; 7130</t>
+          <t>1238; 6995</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14092; 27204</t>
+          <t>13936; 26820</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23967; 38246</t>
+          <t>24176; 38277</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9934; 22256</t>
+          <t>10003; 22050</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4885; 13631</t>
+          <t>4444; 13605</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19778; 49514</t>
+          <t>17578; 47354</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4716; 11487</t>
+          <t>4472; 11330</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2335; 9739</t>
+          <t>2319; 9450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>770; 6035</t>
+          <t>766; 5973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7699; 16385</t>
+          <t>7614; 16028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3299; 10330</t>
+          <t>3835; 10477</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2681; 9661</t>
+          <t>2765; 10001</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2782; 9882</t>
+          <t>2620; 9984</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5741; 14881</t>
+          <t>6162; 14989</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9786; 19437</t>
+          <t>9785; 19415</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6526; 16840</t>
+          <t>6687; 16888</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4626; 13500</t>
+          <t>4502; 13087</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15750; 28494</t>
+          <t>16241; 28658</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1986; 6211</t>
+          <t>2083; 6209</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 3803</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 4351</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2352; 7796</t>
+          <t>2485; 7970</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3494; 8817</t>
+          <t>3467; 8797</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1280; 6592</t>
+          <t>1236; 6147</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>627; 4869</t>
+          <t>630; 4958</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3015; 10181</t>
+          <t>3057; 10028</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6802; 13762</t>
+          <t>6877; 13801</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2063; 8393</t>
+          <t>2056; 8620</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1295; 7223</t>
+          <t>1267; 7081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7108; 16041</t>
+          <t>7049; 15733</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>35827; 52133</t>
+          <t>35112; 51728</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17515; 32330</t>
+          <t>17343; 32587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10469; 21507</t>
+          <t>9517; 20996</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31406; 65916</t>
+          <t>29873; 65217</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43961; 62770</t>
+          <t>44209; 62957</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14312; 28520</t>
+          <t>14336; 30333</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9983; 21515</t>
+          <t>9654; 21391</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>50680; 72167</t>
+          <t>50506; 73775</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>85624; 110210</t>
+          <t>85309; 109750</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36559; 56177</t>
+          <t>35835; 56225</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22383; 38609</t>
+          <t>22335; 38460</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>85890; 131012</t>
+          <t>84347; 130247</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16_n_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>39,28%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>13,42%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46,14%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,79; 59,32</t>
+          <t>15,06; 45,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,41</t>
+          <t>3,05; 30,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 35,54</t>
+          <t>0,0; 21,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,27; 61,38</t>
+          <t>12,65; 43,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 46,4</t>
+          <t>21,03; 59,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,33</t>
+          <t>0,0; 22,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,62</t>
+          <t>3,5; 34,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,47; 43,8</t>
+          <t>31,07; 62,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,15; 46,25</t>
+          <t>22,6; 45,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 19,22</t>
+          <t>3,48; 19,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 21,39</t>
+          <t>3,59; 22,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,56; 47,02</t>
+          <t>24,32; 47,14</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>34,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>16,68%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,11%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>42,12%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,56; 53,8</t>
+          <t>23,26; 62,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 31,5</t>
+          <t>0,0; 27,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,0</t>
+          <t>3,7; 31,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 39,43</t>
+          <t>25,81; 63,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,07; 61,0</t>
+          <t>17,56; 53,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,39</t>
+          <t>6,22; 31,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 33,23</t>
+          <t>0,0; 25,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 60,85</t>
+          <t>12,45; 41,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,58; 52,13</t>
+          <t>26,13; 50,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 23,88</t>
+          <t>5,34; 24,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 22,15</t>
+          <t>4,18; 22,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,37; 47,8</t>
+          <t>23,02; 47,82</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54,57%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,51%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39,22%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>33,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>29,77%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>34,44%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>54,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,7; 57,14</t>
+          <t>37,74; 71,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,25; 59,9</t>
+          <t>5,55; 48,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 63,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 51,75</t>
+          <t>19,3; 62,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,14; 70,59</t>
+          <t>15,46; 58,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 48,62</t>
+          <t>10,22; 53,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,73; 64,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,52; 57,88</t>
+          <t>8,44; 52,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,42; 61,89</t>
+          <t>34,19; 61,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 42,07</t>
+          <t>13,56; 40,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 32,22</t>
+          <t>5,98; 31,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,46; 47,66</t>
+          <t>18,68; 48,62</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40,1%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>39,99%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>18,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,2%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,84; 53,65</t>
+          <t>27,73; 53,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 28,52</t>
+          <t>5,09; 19,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 20,22</t>
+          <t>3,41; 19,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 34,28</t>
+          <t>22,91; 47,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,79; 53,62</t>
+          <t>28,31; 53,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 19,54</t>
+          <t>9,9; 29,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 20,26</t>
+          <t>5,49; 19,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,95; 48,03</t>
+          <t>19,78; 45,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,61; 50,05</t>
+          <t>31,02; 48,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 20,5</t>
+          <t>8,87; 21,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 16,79</t>
+          <t>5,8; 16,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,29; 35,81</t>
+          <t>26,41; 43,5</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22,36%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28,58%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>41,8%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>18,69%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,23%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40,67%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,72; 60,1</t>
+          <t>14,36; 44,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 32,99</t>
+          <t>9,29; 35,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 22,44</t>
+          <t>10,77; 39,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,34; 55,45</t>
+          <t>16,31; 43,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,04; 43,84</t>
+          <t>21,61; 59,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,86; 35,67</t>
+          <t>7,71; 35,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 38,91</t>
+          <t>2,08; 21,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 41,66</t>
+          <t>24,86; 54,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,89; 45,41</t>
+          <t>23,04; 46,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,8; 29,79</t>
+          <t>11,35; 29,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 25,03</t>
+          <t>9,09; 26,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,03; 44,17</t>
+          <t>24,14; 43,57</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54,48%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21,21%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>56,29%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>21,21%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40,85%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,83; 82,97</t>
+          <t>29,79; 77,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,9</t>
+          <t>9,67; 48,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,4</t>
+          <t>6,28; 48,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,33; 65,22</t>
+          <t>18,55; 65,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,58; 77,6</t>
+          <t>27,86; 83,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 44,56</t>
+          <t>0,0; 56,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,44; 50,71</t>
+          <t>0,0; 32,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,98; 65,54</t>
+          <t>17,37; 63,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,54; 73,33</t>
+          <t>35,42; 73,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,86; 41,34</t>
+          <t>9,87; 40,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 31,05</t>
+          <t>6,02; 33,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,62; 57,17</t>
+          <t>26,24; 57,75</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39,92%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14,38%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>39,8%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>17,49%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>12,09%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39,92%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,0; 47,14</t>
+          <t>33,2; 46,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,42; 23,34</t>
+          <t>9,74; 19,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,75; 17,1</t>
+          <t>8,47; 18,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,03; 37,18</t>
+          <t>27,94; 41,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,68; 46,53</t>
+          <t>32,24; 47,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 20,59</t>
+          <t>12,69; 22,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,25; 18,28</t>
+          <t>8,02; 16,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,17; 41,14</t>
+          <t>28,32; 41,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,82; 44,79</t>
+          <t>34,77; 45,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,49; 19,6</t>
+          <t>12,85; 20,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,31; 16,03</t>
+          <t>9,55; 16,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,78; 36,72</t>
+          <t>30,48; 39,22</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7521</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5959</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1467</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2126</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11466</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6099</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2450</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>19123</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3305; 9000</t>
+          <t>3232; 9810</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4479</t>
+          <t>671; 6757</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>557; 5631</t>
+          <t>0; 3893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7771; 15254</t>
+          <t>3649; 12683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3296; 9958</t>
+          <t>3190; 9074</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>668; 6007</t>
+          <t>0; 4629</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4015</t>
+          <t>554; 5508</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4231; 13752</t>
+          <t>7656; 15517</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7746; 16942</t>
+          <t>8279; 16506</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1425; 8247</t>
+          <t>1491; 8493</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1177; 7184</t>
+          <t>1207; 7445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13816; 26451</t>
+          <t>13004; 25212</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7521</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9911</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6796</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3820</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5672</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7521</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2754</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15498</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3800; 10454</t>
+          <t>4154; 11146</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1731; 7215</t>
+          <t>0; 3267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3119</t>
+          <t>705; 6088</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2581; 9240</t>
+          <t>5841; 14340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4477; 10893</t>
+          <t>3411; 10416</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3311</t>
+          <t>1425; 7207</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>713; 6335</t>
+          <t>0; 3001</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6119; 14295</t>
+          <t>2860; 9633</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9912; 19436</t>
+          <t>9744; 18834</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1834; 8355</t>
+          <t>1868; 8622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1270; 6878</t>
+          <t>1298; 6852</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10967; 22431</t>
+          <t>10498; 21807</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11980</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5892</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3758</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3415</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3047</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>11980</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2684</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8149</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1522; 6348</t>
+          <t>8284; 15677</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1520; 6871</t>
+          <t>693; 6049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1203; 5628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>617; 4966</t>
+          <t>2900; 9368</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7713; 15496</t>
+          <t>1717; 6504</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>719; 6067</t>
+          <t>1173; 6128</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1126; 5736</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3204; 10011</t>
+          <t>803; 5012</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11381; 20463</t>
+          <t>11304; 20387</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2981; 10076</t>
+          <t>3248; 9761</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1091; 6158</t>
+          <t>1143; 6042</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4965; 12818</t>
+          <t>4585; 11933</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15555</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17658</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15072</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8871</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5206</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14493</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15555</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6501</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3202</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>31642</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10492; 20218</t>
+          <t>10757; 20656</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5178; 13875</t>
+          <t>2996; 11322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2461; 9400</t>
+          <t>1179; 6798</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5093; 26185</t>
+          <t>11397; 23632</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10391; 20799</t>
+          <t>10669; 20344</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3162; 11512</t>
+          <t>4813; 14225</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1238; 6995</t>
+          <t>2552; 9257</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13936; 26820</t>
+          <t>8416; 19145</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24176; 38277</t>
+          <t>23720; 37392</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10003; 22050</t>
+          <t>9535; 22764</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4444; 13605</t>
+          <t>4698; 13447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17578; 47354</t>
+          <t>24370; 40145</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6685</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5581</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5738</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9195</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>7881</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>5355</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2456</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11756</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6685</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5581</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5738</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>20439</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4472; 11330</t>
+          <t>3432; 10728</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2319; 9450</t>
+          <t>2606; 9854</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>766; 5973</t>
+          <t>2765; 10215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7614; 16028</t>
+          <t>5245; 13916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3835; 10477</t>
+          <t>4074; 11188</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2765; 10001</t>
+          <t>2208; 10161</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2620; 9984</t>
+          <t>553; 5617</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6162; 14989</t>
+          <t>7113; 15528</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9785; 19415</t>
+          <t>9850; 20004</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6687; 16888</t>
+          <t>6435; 16688</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4502; 13087</t>
+          <t>4751; 13677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16241; 28658</t>
+          <t>14671; 26483</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5777</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>4212</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1497</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1407</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4992</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6177</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>10732</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2083; 6209</t>
+          <t>3377; 8824</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3803</t>
+          <t>1335; 6680</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4351</t>
+          <t>614; 4737</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2485; 7970</t>
+          <t>2619; 9256</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3467; 8797</t>
+          <t>2085; 6216</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1236; 6147</t>
+          <t>0; 3972</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>630; 4958</t>
+          <t>0; 4263</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3057; 10028</t>
+          <t>2162; 7869</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6877; 13801</t>
+          <t>6667; 13811</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2056; 8620</t>
+          <t>2059; 8509</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1267; 7081</t>
+          <t>1372; 7654</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7049; 15733</t>
+          <t>6970; 15340</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>54017</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21177</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15051</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>55954</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>43678</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>24424</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>14855</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>54017</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>21177</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15051</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>35112; 51728</t>
+          <t>44920; 63485</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17343; 32587</t>
+          <t>14352; 28304</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9517; 20996</t>
+          <t>9914; 21765</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29873; 65217</t>
+          <t>45411; 67515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44209; 62957</t>
+          <t>35378; 51958</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14336; 30333</t>
+          <t>17718; 32088</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9654; 21391</t>
+          <t>9846; 20796</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>50506; 73775</t>
+          <t>39857; 58548</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>85309; 109750</t>
+          <t>85197; 110405</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35835; 56225</t>
+          <t>36863; 58187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22335; 38460</t>
+          <t>22903; 39222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>84347; 130247</t>
+          <t>92426; 118942</t>
         </is>
       </c>
     </row>
